--- a/output/Data and Chart Outputs/japan_fx_usd_daily.xlsx
+++ b/output/Data and Chart Outputs/japan_fx_usd_daily.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$C$2:$C$1440</f>
+              <f>'Chart'!$C$2:$C$1454</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$1440</f>
+              <f>'Chart'!$B$2:$B$1454</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -679,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1440"/>
+  <dimension ref="A1:C1454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12302,6 +12302,118 @@
       </c>
       <c r="B1440" t="n">
         <v>157.81</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1441" t="n">
+        <v>157.97</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1442" t="n">
+        <v>158.12</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1443" t="n">
+        <v>158.11</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1444" t="n">
+        <v>158.33</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1445" t="n">
+        <v>158.34</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1446" t="n">
+        <v>158.36</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1447" t="n">
+        <v>158.84</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1448" t="n">
+        <v>158.18</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1449" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1450" t="n">
+        <v>158.49</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1451" t="n">
+        <v>158.2</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1452" t="n">
+        <v>158.13</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1453" t="n">
+        <v>157.11</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1454" t="n">
+        <v>156.87</v>
       </c>
     </row>
   </sheetData>
@@ -12316,7 +12428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2688"/>
+  <dimension ref="A1:C2702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33832,6 +33944,118 @@
         <v>157.81</v>
       </c>
     </row>
+    <row r="2689">
+      <c r="A2689" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B2689" t="n">
+        <v>157.97</v>
+      </c>
+    </row>
+    <row r="2690">
+      <c r="A2690" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2690" t="n">
+        <v>158.12</v>
+      </c>
+    </row>
+    <row r="2691">
+      <c r="A2691" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2691" t="n">
+        <v>158.11</v>
+      </c>
+    </row>
+    <row r="2692">
+      <c r="A2692" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2692" t="n">
+        <v>158.33</v>
+      </c>
+    </row>
+    <row r="2693">
+      <c r="A2693" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2693" t="n">
+        <v>158.34</v>
+      </c>
+    </row>
+    <row r="2694">
+      <c r="A2694" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2694" t="n">
+        <v>158.36</v>
+      </c>
+    </row>
+    <row r="2695">
+      <c r="A2695" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2695" t="n">
+        <v>158.84</v>
+      </c>
+    </row>
+    <row r="2696">
+      <c r="A2696" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2696" t="n">
+        <v>158.18</v>
+      </c>
+    </row>
+    <row r="2697">
+      <c r="A2697" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2697" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2698">
+      <c r="A2698" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2698" t="n">
+        <v>158.49</v>
+      </c>
+    </row>
+    <row r="2699">
+      <c r="A2699" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B2699" t="n">
+        <v>158.2</v>
+      </c>
+    </row>
+    <row r="2700">
+      <c r="A2700" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2700" t="n">
+        <v>158.13</v>
+      </c>
+    </row>
+    <row r="2701">
+      <c r="A2701" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B2701" t="n">
+        <v>157.11</v>
+      </c>
+    </row>
+    <row r="2702">
+      <c r="A2702" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B2702" t="n">
+        <v>156.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
